--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260617.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.28%</t>
+          <t>10.26%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>885,744,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>10.22%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>6.92%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
@@ -704,161 +704,161 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>112,424,000</t>
+          <t>4,989,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,989,000</t>
+          <t>112,424,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,186</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>2,036</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>28,485,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>134,180,945</t>
+          <t>28,485,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>134,180,945</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -946,24 +946,24 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>25,874,000</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,22 +975,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>25,874,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>339,675,000</t>
+          <t>344,175,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>50,247,000</t>
+          <t>50,567,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>14,243,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,653,713,658</t>
+          <t>10,255,552,642</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,645,854,048</t>
+          <t>10,716,618,559</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-1,998,118,917</t>
+          <t>-2,351,121,372</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
